--- a/artfynd/A 26849-2023 artfynd.xlsx
+++ b/artfynd/A 26849-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126229216</v>
       </c>
       <c r="B2" t="n">
-        <v>106808</v>
+        <v>106812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26849-2023 artfynd.xlsx
+++ b/artfynd/A 26849-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126229216</v>
       </c>
       <c r="B2" t="n">
-        <v>106812</v>
+        <v>106825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26849-2023 artfynd.xlsx
+++ b/artfynd/A 26849-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126229216</v>
       </c>
       <c r="B2" t="n">
-        <v>106825</v>
+        <v>106828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26849-2023 artfynd.xlsx
+++ b/artfynd/A 26849-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126229216</v>
       </c>
       <c r="B2" t="n">
-        <v>106828</v>
+        <v>106837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 26849-2023 artfynd.xlsx
+++ b/artfynd/A 26849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126229216</v>
       </c>
       <c r="B2" t="n">
-        <v>106837</v>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,6 +796,134 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126229207</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hasselbol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>404024</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6605802</v>
+      </c>
+      <c r="S3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Kil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I inner- och ytterslänt på norra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
